--- a/probabilidades_mundial.xlsx
+++ b/probabilidades_mundial.xlsx
@@ -463,19 +463,19 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>83.3</v>
+        <v>87</v>
       </c>
       <c r="D2" t="n">
-        <v>58.2</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>50.9</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>37.1</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>23.4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3" t="n">
         <v>77</v>
       </c>
-      <c r="D3" t="n">
-        <v>68.5</v>
-      </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>34.5</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>21.8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -510,591 +510,591 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>99.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="C4" t="n">
-        <v>83.8</v>
+        <v>77</v>
       </c>
       <c r="D4" t="n">
-        <v>66.8</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>27.9</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
-        <v>76.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>50.6</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
-        <v>32.2</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>70.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="D6" t="n">
-        <v>52.3</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
-        <v>29.7</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>12.2</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>60.4</v>
+        <v>82</v>
       </c>
       <c r="D7" t="n">
-        <v>36.6</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>20.5</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>75.90000000000001</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>45.9</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>10.7</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>69.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="D9" t="n">
-        <v>36.1</v>
+        <v>41</v>
       </c>
       <c r="E9" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="C10" t="n">
-        <v>61.2</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>31.5</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>15.2</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>97.7</v>
+        <v>97</v>
       </c>
       <c r="C11" t="n">
-        <v>54.4</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>24.2</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99.8</v>
+        <v>89</v>
       </c>
       <c r="C12" t="n">
-        <v>74.8</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>34.6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>12.6</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>92.8</v>
+        <v>88</v>
       </c>
       <c r="C13" t="n">
-        <v>61.1</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>30.8</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>26.5</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>11.1</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>97</v>
       </c>
       <c r="C15" t="n">
-        <v>61.9</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>25.9</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="C16" t="n">
-        <v>23.9</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94.8</v>
+        <v>88</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>21.1</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>7.9</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>98.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="C18" t="n">
-        <v>52.9</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>22.3</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="C19" t="n">
-        <v>51.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>21.7</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93.3</v>
+        <v>85</v>
       </c>
       <c r="C20" t="n">
-        <v>46.7</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>12.9</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>98.2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>59.6</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>60.4</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>26.4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>91.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="C23" t="n">
-        <v>29.9</v>
+        <v>54</v>
       </c>
       <c r="D23" t="n">
-        <v>11.2</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>80.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>83.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="C25" t="n">
-        <v>31.3</v>
+        <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>88.09999999999999</v>
+        <v>30</v>
       </c>
       <c r="C26" t="n">
-        <v>41.5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>10.7</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.5</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1106,20 +1106,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34.9</v>
+        <v>97</v>
       </c>
       <c r="C28" t="n">
-        <v>5.4</v>
+        <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>10.7</v>
+        <v>15</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1156,23 +1156,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>36.4</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>6.3</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1181,20 +1181,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>66.7</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1206,20 +1206,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1231,14 +1231,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7.7</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>61.6</v>
+        <v>69</v>
       </c>
       <c r="C34" t="n">
-        <v>16.6</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1285,16 +1285,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>48.2</v>
+        <v>49</v>
       </c>
       <c r="C35" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35.7</v>
+        <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1331,23 +1331,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C37" t="n">
+        <v>48</v>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="E37" t="n">
-        <v>0.1</v>
-      </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1356,23 +1356,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.2</v>
+        <v>99</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2</v>
+        <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1381,17 +1381,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6</v>
+        <v>29</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23.7</v>
+        <v>26</v>
       </c>
       <c r="C41" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1460,19 +1460,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>87.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="C42" t="n">
-        <v>34.2</v>
+        <v>37</v>
       </c>
       <c r="D42" t="n">
         <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>80.3</v>
+        <v>74</v>
       </c>
       <c r="C44" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D44" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1535,19 +1535,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>77.3</v>
+        <v>78</v>
       </c>
       <c r="C45" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>6.1</v>
+        <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.3</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>38.8</v>
+        <v>43</v>
       </c>
       <c r="C48" t="n">
-        <v>13.8</v>
+        <v>21</v>
       </c>
       <c r="D48" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1635,16 +1635,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>68.09999999999999</v>
+        <v>63</v>
       </c>
       <c r="C49" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
